--- a/data/filtered/china_biography.xlsx
+++ b/data/filtered/china_biography.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I172"/>
+  <dimension ref="A1:N172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,31 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>是否春节档</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>是否国庆档</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>是否五一档</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>是否暑期档</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>是否普通周末</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>详情链接</t>
         </is>
       </c>
@@ -498,7 +523,22 @@
           <t>1987-10-04</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1293172/</t>
         </is>
@@ -539,7 +579,22 @@
           <t>1997-05-15</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1303913/</t>
         </is>
@@ -580,7 +635,22 @@
           <t>2019-03-01</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27060077/</t>
         </is>
@@ -621,7 +691,22 @@
           <t>2006-10-24</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3097352/</t>
         </is>
@@ -662,7 +747,22 @@
           <t>2003</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5301572/</t>
         </is>
@@ -703,7 +803,22 @@
           <t>1985-08-03</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1300572/</t>
         </is>
@@ -744,7 +859,22 @@
           <t>1991-11-29</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1293414/</t>
         </is>
@@ -785,7 +915,22 @@
           <t>2001-09-04</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1308086/</t>
         </is>
@@ -826,7 +971,22 @@
           <t>1999-09-16</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1316511/</t>
         </is>
@@ -867,7 +1027,22 @@
           <t>2009-03-19</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3737287/</t>
         </is>
@@ -908,7 +1083,22 @@
           <t>1992-01-09</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1448751/</t>
         </is>
@@ -949,7 +1139,22 @@
           <t>1991-04-15</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1296272/</t>
         </is>
@@ -990,7 +1195,22 @@
           <t>2013-01-08</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3821067/</t>
         </is>
@@ -1031,7 +1251,22 @@
           <t>2007-12-20</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1907464/</t>
         </is>
@@ -1072,7 +1307,22 @@
           <t>1993-05-24</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1302941/</t>
         </is>
@@ -1113,7 +1363,22 @@
           <t>2002-10-09</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1296769/</t>
         </is>
@@ -1154,7 +1419,22 @@
           <t>2008-12-12</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3041806/</t>
         </is>
@@ -1195,7 +1475,22 @@
           <t>2022-10-01</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35358429/</t>
         </is>
@@ -1236,7 +1531,22 @@
           <t>1994-02-26</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1295299/</t>
         </is>
@@ -1277,7 +1587,22 @@
           <t>1990</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1439400/</t>
         </is>
@@ -1318,7 +1643,22 @@
           <t>2009-04-29</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2294565/</t>
         </is>
@@ -1359,7 +1699,22 @@
           <t>2005-08-05</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1483630/</t>
         </is>
@@ -1400,7 +1755,22 @@
           <t>2010-04-27</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3578981/</t>
         </is>
@@ -1441,7 +1811,22 @@
           <t>2019-12-24</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26848640/</t>
         </is>
@@ -1482,7 +1867,22 @@
           <t>2014-10-01</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10545939/</t>
         </is>
@@ -1523,7 +1923,22 @@
           <t>1987-10-24</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1300038/</t>
         </is>
@@ -1564,7 +1979,22 @@
           <t>2012-03-02</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6041200/</t>
         </is>
@@ -1605,7 +2035,22 @@
           <t>1994-03-12</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1297514/</t>
         </is>
@@ -1646,7 +2091,22 @@
           <t>2006-01-25</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1441602/</t>
         </is>
@@ -1687,7 +2147,22 @@
           <t>2012-03-08</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6078003/</t>
         </is>
@@ -1728,7 +2203,22 @@
           <t>1990-07-28</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1307569/</t>
         </is>
@@ -1769,7 +2259,22 @@
           <t>2017-09-08</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26704137/</t>
         </is>
@@ -1810,7 +2315,22 @@
           <t>1988-11-10</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1296044/</t>
         </is>
@@ -1851,7 +2371,22 @@
           <t>1955</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1482709/</t>
         </is>
@@ -1892,7 +2427,22 @@
           <t>2015-09-10</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26440017/</t>
         </is>
@@ -1933,7 +2483,22 @@
           <t>1996-03-04</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2148619/</t>
         </is>
@@ -1974,7 +2539,22 @@
           <t>1951-02-21</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1432824/</t>
         </is>
@@ -2015,7 +2595,22 @@
           <t>1991-04-12</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1305720/</t>
         </is>
@@ -2056,7 +2651,22 @@
           <t>1959</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1308306/</t>
         </is>
@@ -2097,7 +2707,22 @@
           <t>2018-03-02</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26995719/</t>
         </is>
@@ -2138,7 +2763,22 @@
           <t>2008-12-05</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1891179/</t>
         </is>
@@ -2179,7 +2819,22 @@
           <t>2011-07-19</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6519575/</t>
         </is>
@@ -2220,7 +2875,22 @@
           <t>1956</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1438024/</t>
         </is>
@@ -2261,7 +2931,22 @@
           <t>2021-08-06</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35132974/</t>
         </is>
@@ -2302,7 +2987,22 @@
           <t>2021-11-12</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30176790/</t>
         </is>
@@ -2343,7 +3043,22 @@
           <t>2016-03-04</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/11598977/</t>
         </is>
@@ -2384,7 +3099,22 @@
           <t>2015-12-18</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26687580/</t>
         </is>
@@ -2425,7 +3155,22 @@
           <t>2006-09-30</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1461370/</t>
         </is>
@@ -2466,7 +3211,22 @@
           <t>2021-09-04</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/32568661/</t>
         </is>
@@ -2507,7 +3267,22 @@
           <t>2019-09-30</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30295905/</t>
         </is>
@@ -2548,7 +3323,22 @@
           <t>2019-10-06</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/32491917/</t>
         </is>
@@ -2589,7 +3379,22 @@
           <t>2023-11-17</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34852932/</t>
         </is>
@@ -2630,7 +3435,22 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1765609/</t>
         </is>
@@ -2671,7 +3491,22 @@
           <t>1986-03-27</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1303503/</t>
         </is>
@@ -2712,7 +3547,22 @@
           <t>2011-06-29</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5343629/</t>
         </is>
@@ -2753,7 +3603,22 @@
           <t>2013-03-08</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6781971/</t>
         </is>
@@ -2794,7 +3659,22 @@
           <t>2020-09-18</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27073179/</t>
         </is>
@@ -2835,7 +3715,22 @@
           <t>1988-09-15</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1308492/</t>
         </is>
@@ -2876,7 +3771,22 @@
           <t>2025-06-27</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35370668/</t>
         </is>
@@ -2917,7 +3827,22 @@
           <t>2012-06-19</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10774103/</t>
         </is>
@@ -2958,7 +3883,22 @@
           <t>2011-12-17</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1</v>
+      </c>
+      <c r="N62" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26803826/</t>
         </is>
@@ -2999,7 +3939,22 @@
           <t>2010-10-26</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4896295/</t>
         </is>
@@ -3040,7 +3995,22 @@
           <t>2019-09-20</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30481973/</t>
         </is>
@@ -3081,7 +4051,22 @@
           <t>2017-10-13</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26689487/</t>
         </is>
@@ -3122,7 +4107,22 @@
           <t>2005-09-09</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1459399/</t>
         </is>
@@ -3163,7 +4163,22 @@
           <t>1940-12-19</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2295854/</t>
         </is>
@@ -3204,7 +4219,22 @@
           <t>1965-03-05</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1472234/</t>
         </is>
@@ -3245,7 +4275,22 @@
           <t>2013-03-22</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10794042/</t>
         </is>
@@ -3286,7 +4331,22 @@
           <t>1987-09-05</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1</v>
+      </c>
+      <c r="N70" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1308553/</t>
         </is>
@@ -3327,7 +4387,22 @@
           <t>2004-08-20</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>1</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1464134/</t>
         </is>
@@ -3368,7 +4443,22 @@
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/33414470/</t>
         </is>
@@ -3409,7 +4499,22 @@
           <t>2015-12-18</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26691500/</t>
         </is>
@@ -3450,7 +4555,22 @@
           <t>2010-11-25</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4915135/</t>
         </is>
@@ -3491,7 +4611,22 @@
           <t>2008-10-17</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3010415/</t>
         </is>
@@ -3532,7 +4667,22 @@
           <t>2018-08-08</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>1</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27104330/</t>
         </is>
@@ -3573,7 +4723,22 @@
           <t>2011-05-13</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5915794/</t>
         </is>
@@ -3614,7 +4779,22 @@
           <t>2017-05-27</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1</v>
+      </c>
+      <c r="N78" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26385746/</t>
         </is>
@@ -3655,7 +4835,22 @@
           <t>2011-10-13</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5924360/</t>
         </is>
@@ -3696,7 +4891,22 @@
           <t>1955</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2136122/</t>
         </is>
@@ -3737,7 +4947,22 @@
           <t>1996-06-17</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1464171/</t>
         </is>
@@ -3778,7 +5003,22 @@
           <t>1993</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1456053/</t>
         </is>
@@ -3819,7 +5059,22 @@
           <t>2020-09-06</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1</v>
+      </c>
+      <c r="N83" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35061627/</t>
         </is>
@@ -3860,7 +5115,22 @@
           <t>1999-10-07</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1868115/</t>
         </is>
@@ -3901,7 +5171,22 @@
           <t>1958</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2375631/</t>
         </is>
@@ -3942,7 +5227,22 @@
           <t>2009</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3647073/</t>
         </is>
@@ -3983,7 +5283,22 @@
           <t>1986-04-24</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4189670/</t>
         </is>
@@ -4024,7 +5339,22 @@
           <t>1988-09-23</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1305979/</t>
         </is>
@@ -4065,7 +5395,22 @@
           <t>2021-05-21</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30347930/</t>
         </is>
@@ -4106,7 +5451,22 @@
           <t>1977-03-31</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1480492/</t>
         </is>
@@ -4147,7 +5507,22 @@
           <t>1992-05-09</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1</v>
+      </c>
+      <c r="N91" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1440736/</t>
         </is>
@@ -4188,7 +5563,22 @@
           <t>2001-12-22</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1</v>
+      </c>
+      <c r="N92" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1422970/</t>
         </is>
@@ -4229,7 +5619,22 @@
           <t>2017-06-30</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27067697/</t>
         </is>
@@ -4270,7 +5675,22 @@
           <t>2009-10-29</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4116995/</t>
         </is>
@@ -4311,7 +5731,22 @@
           <t>2010-01-22</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3606975/</t>
         </is>
@@ -4352,7 +5787,22 @@
           <t>2020-08-25</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>1</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30353078/</t>
         </is>
@@ -4393,7 +5843,22 @@
           <t>1995</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1298490/</t>
         </is>
@@ -4434,7 +5899,22 @@
           <t>2003-02-19</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1464141/</t>
         </is>
@@ -4475,7 +5955,22 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30291567/</t>
         </is>
@@ -4516,7 +6011,22 @@
           <t>1983</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1483982/</t>
         </is>
@@ -4557,7 +6067,22 @@
           <t>2019-10-04</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>1</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34845519/</t>
         </is>
@@ -4598,7 +6123,22 @@
           <t>2017-05-19</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26794232/</t>
         </is>
@@ -4639,7 +6179,22 @@
           <t>1992</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1464592/</t>
         </is>
@@ -4680,7 +6235,22 @@
           <t>1983</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2261764/</t>
         </is>
@@ -4721,7 +6291,22 @@
           <t>2019-10-07</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>1</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/33447759/</t>
         </is>
@@ -4762,7 +6347,22 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30307233/</t>
         </is>
@@ -4803,7 +6403,22 @@
           <t>1962-05-31</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1299090/</t>
         </is>
@@ -4844,7 +6459,22 @@
           <t>1950</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1968505/</t>
         </is>
@@ -4885,7 +6515,22 @@
           <t>1993</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1919408/</t>
         </is>
@@ -4926,7 +6571,22 @@
           <t>1981</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3264844/</t>
         </is>
@@ -4967,7 +6627,22 @@
           <t>1963-12-28</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="n">
+        <v>1</v>
+      </c>
+      <c r="N111" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1461917/</t>
         </is>
@@ -5008,7 +6683,22 @@
           <t>2023-08-31</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="n">
+        <v>1</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26368295/</t>
         </is>
@@ -5049,7 +6739,22 @@
           <t>2018-08-24</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
+        <v>1</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30244759/</t>
         </is>
@@ -5090,7 +6795,22 @@
           <t>1952</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1962574/</t>
         </is>
@@ -5131,7 +6851,22 @@
           <t>2011-06-17</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3732536/</t>
         </is>
@@ -5172,7 +6907,22 @@
           <t>1985</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1915869/</t>
         </is>
@@ -5213,7 +6963,22 @@
           <t>2011-04-26</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4821046/</t>
         </is>
@@ -5254,7 +7019,22 @@
           <t>2017-08-14</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="n">
+        <v>1</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27119392/</t>
         </is>
@@ -5295,7 +7075,22 @@
           <t>2019-09-09</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/33434919/</t>
         </is>
@@ -5336,7 +7131,22 @@
           <t>2005-07-01</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>1</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1440095/</t>
         </is>
@@ -5377,7 +7187,22 @@
           <t>1986</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1864713/</t>
         </is>
@@ -5418,7 +7243,22 @@
           <t>1979</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1464571/</t>
         </is>
@@ -5459,7 +7299,22 @@
           <t>2007-06-28</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2153250/</t>
         </is>
@@ -5500,7 +7355,22 @@
           <t>2013</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30290562/</t>
         </is>
@@ -5541,7 +7411,22 @@
           <t>1996</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2046967/</t>
         </is>
@@ -5582,7 +7467,22 @@
           <t>1998-09-18</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1400123/</t>
         </is>
@@ -5623,7 +7523,22 @@
           <t>2003</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2378660/</t>
         </is>
@@ -5664,7 +7579,22 @@
           <t>2012-01-14</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="n">
+        <v>1</v>
+      </c>
+      <c r="N128" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10461347/</t>
         </is>
@@ -5705,7 +7635,22 @@
           <t>2013</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30292834/</t>
         </is>
@@ -5746,7 +7691,22 @@
           <t>2011-10-13</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6528885/</t>
         </is>
@@ -5787,7 +7747,22 @@
           <t>2013</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/19971608/</t>
         </is>
@@ -5828,7 +7803,22 @@
           <t>2008-11-12</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4022125/</t>
         </is>
@@ -5869,7 +7859,22 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3080197/</t>
         </is>
@@ -5910,7 +7915,22 @@
           <t>1984-08-30</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="n">
+        <v>1</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2224796/</t>
         </is>
@@ -5951,7 +7971,22 @@
           <t>1990-08-27</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="n">
+        <v>1</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1891222/</t>
         </is>
@@ -5992,7 +8027,22 @@
           <t>2007-11-21</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr">
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2246605/</t>
         </is>
@@ -6033,7 +8083,22 @@
           <t>1958</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1946309/</t>
         </is>
@@ -6074,7 +8139,22 @@
           <t>1976-10-28</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr">
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2277993/</t>
         </is>
@@ -6115,7 +8195,22 @@
           <t>2012</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10740288/</t>
         </is>
@@ -6156,7 +8251,22 @@
           <t>2012-10-14</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>1</v>
+      </c>
+      <c r="N140" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/19977901/</t>
         </is>
@@ -6197,7 +8307,22 @@
           <t>2006-08-29</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="n">
+        <v>1</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1915339/</t>
         </is>
@@ -6238,7 +8363,22 @@
           <t>2004-08-20</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr">
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="n">
+        <v>1</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2252751/</t>
         </is>
@@ -6279,7 +8419,22 @@
           <t>2016-07-01</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" t="n">
+        <v>1</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25927500/</t>
         </is>
@@ -6320,7 +8475,22 @@
           <t>1981</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr">
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3254213/</t>
         </is>
@@ -6361,7 +8531,22 @@
           <t>2011-07-15</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr">
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="n">
+        <v>1</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6013758/</t>
         </is>
@@ -6402,7 +8587,22 @@
           <t>2001-09-22</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" t="n">
+        <v>1</v>
+      </c>
+      <c r="N146" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1930735/</t>
         </is>
@@ -6443,7 +8643,22 @@
           <t>1950</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0</v>
+      </c>
+      <c r="N147" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2160551/</t>
         </is>
@@ -6484,7 +8699,22 @@
           <t>1993</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr">
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0</v>
+      </c>
+      <c r="N148" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4004940/</t>
         </is>
@@ -6525,7 +8755,22 @@
           <t>2014</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr">
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0</v>
+      </c>
+      <c r="N149" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26323543/</t>
         </is>
@@ -6566,7 +8811,22 @@
           <t>2013-10-01</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr">
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
+        <v>1</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/24860303/</t>
         </is>
@@ -6607,7 +8867,22 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr">
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25700831/</t>
         </is>
@@ -6648,7 +8923,22 @@
           <t>2022-07-05</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr">
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" t="n">
+        <v>1</v>
+      </c>
+      <c r="M152" t="n">
+        <v>0</v>
+      </c>
+      <c r="N152" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35801555/</t>
         </is>
@@ -6689,7 +8979,22 @@
           <t>1985</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr">
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4290614/</t>
         </is>
@@ -6730,7 +9035,22 @@
           <t>2016-09-13</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr">
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/22552302/</t>
         </is>
@@ -6771,7 +9091,22 @@
           <t>2018-12-12</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr">
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" t="n">
+        <v>0</v>
+      </c>
+      <c r="N155" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30185236/</t>
         </is>
@@ -6812,7 +9147,22 @@
           <t>2010-10-15</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr">
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5299036/</t>
         </is>
@@ -6853,7 +9203,22 @@
           <t>2019-05-17</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr">
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27187926/</t>
         </is>
@@ -6894,7 +9259,22 @@
           <t>2011-09-30</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr">
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="n">
+        <v>1</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5997856/</t>
         </is>
@@ -6931,7 +9311,22 @@
           <t>2015-12-24</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0</v>
+      </c>
+      <c r="N159" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26691703/</t>
         </is>
@@ -6972,7 +9367,22 @@
           <t>2012</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr">
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/11499793/</t>
         </is>
@@ -7013,7 +9423,22 @@
           <t>1976-01-09</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr">
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1304134/</t>
         </is>
@@ -7054,7 +9479,22 @@
           <t>2012-10-12</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr">
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/11627084/</t>
         </is>
@@ -7095,7 +9535,22 @@
           <t>1992</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr">
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1980954/</t>
         </is>
@@ -7136,7 +9591,22 @@
           <t>2018-04-01</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" t="n">
+        <v>1</v>
+      </c>
+      <c r="N164" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30185514/</t>
         </is>
@@ -7177,7 +9647,22 @@
           <t>2019-12-23</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr">
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0</v>
+      </c>
+      <c r="N165" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34678997/</t>
         </is>
@@ -7218,7 +9703,22 @@
           <t>2018-11-21</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr">
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" t="n">
+        <v>0</v>
+      </c>
+      <c r="N166" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27068535/</t>
         </is>
@@ -7259,7 +9759,22 @@
           <t>2013-12-26</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr">
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/24551558/</t>
         </is>
@@ -7300,7 +9815,22 @@
           <t>2013-03-05</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr">
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0</v>
+      </c>
+      <c r="N168" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20438460/</t>
         </is>
@@ -7341,7 +9871,22 @@
           <t>2013-03-05</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr">
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/21363244/</t>
         </is>
@@ -7382,7 +9927,22 @@
           <t>2013</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr">
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L170" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" t="n">
+        <v>0</v>
+      </c>
+      <c r="N170" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20388219/</t>
         </is>
@@ -7423,7 +9983,22 @@
           <t>2013-03-04</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr">
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="n">
+        <v>0</v>
+      </c>
+      <c r="L171" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" t="n">
+        <v>0</v>
+      </c>
+      <c r="N171" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/11627079/</t>
         </is>
@@ -7460,7 +10035,22 @@
           <t>2012-06-01</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr">
+      <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="n">
+        <v>0</v>
+      </c>
+      <c r="L172" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" t="n">
+        <v>0</v>
+      </c>
+      <c r="N172" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10757012/</t>
         </is>
